--- a/survey_templates/040_snake_awareness_quiz--survey_templates.xlsx
+++ b/survey_templates/040_snake_awareness_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'a)_to_educate_students_about_snake_safety'}</t>
+          <t>a)_to_educate_students_about_snake_safety</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'A) To educate students about snake safety'}</t>
+          <t>A) To educate students about snake safety</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'b)_to_entertain_students_with_a_fun_quiz'}</t>
+          <t>b)_to_entertain_students_with_a_fun_quiz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'B) To entertain students with a fun quiz'}</t>
+          <t>B) To entertain students with a fun quiz</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'c)_to_track_student_progress_and_improve_training_for_field_activities'}</t>
+          <t>c)_to_track_student_progress_and_improve_training_for_field_activities</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'C) To track student progress and improve training for field activities'}</t>
+          <t>C) To track student progress and improve training for field activities</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'d)_to_test_student_knowledge_on_outdoor_safety'}</t>
+          <t>d)_to_test_student_knowledge_on_outdoor_safety</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'D) To test student knowledge on outdoor safety'}</t>
+          <t>D) To test student knowledge on outdoor safety</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'hiking_or_backpacking'}</t>
+          <t>hiking_or_backpacking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Hiking or backpacking'}</t>
+          <t>Hiking or backpacking</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'near_water_sources'}</t>
+          <t>near_water_sources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Near water sources'}</t>
+          <t>Near water sources</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'in_rocky_or_brushy_areas'}</t>
+          <t>in_rocky_or_brushy_areas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'In rocky or brushy areas'}</t>
+          <t>In rocky or brushy areas</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'near_tall_grass_or_weeds'}</t>
+          <t>near_tall_grass_or_weeds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Near tall grass or weeds'}</t>
+          <t>Near tall grass or weeds</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'in_urban_areas'}</t>
+          <t>in_urban_areas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'In urban areas'}</t>
+          <t>In urban areas</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'color_and_pattern'}</t>
+          <t>color_and_pattern</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'Color and pattern'}</t>
+          <t>Color and pattern</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'size_and_shape'}</t>
+          <t>size_and_shape</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'Size and shape'}</t>
+          <t>Size and shape</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'movement_and_behavior'}</t>
+          <t>movement_and_behavior</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'Movement and behavior'}</t>
+          <t>Movement and behavior</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'all_of_the_above'}</t>
+          <t>all_of_the_above</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'All of the above'}</t>
+          <t>All of the above</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'run_away_quickly'}</t>
+          <t>run_away_quickly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Run away quickly'}</t>
+          <t>Run away quickly</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'stay_calm_and_observe'}</t>
+          <t>stay_calm_and_observe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'Stay calm and observe'}</t>
+          <t>Stay calm and observe</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'slowly_back_away_with_a_firm_but_calm_voice'}</t>
+          <t>slowly_back_away_with_a_firm_but_calm_voice</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Slowly back away with a firm but calm voice'}</t>
+          <t>Slowly back away with a firm but calm voice</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'fight_the_snake_with_a_stick_or_object'}</t>
+          <t>fight_the_snake_with_a_stick_or_object</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'Fight the snake with a stick or object'}</t>
+          <t>Fight the snake with a stick or object</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'touch_it_gently_with_your_hands'}</t>
+          <t>touch_it_gently_with_your_hands</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'Touch it gently with your hands'}</t>
+          <t>Touch it gently with your hands</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'slowly_back_away_and_observe_from_a_distance'}</t>
+          <t>slowly_back_away_and_observe_from_a_distance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'Slowly back away and observe from a distance'}</t>
+          <t>Slowly back away and observe from a distance</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_'try_to_pick_it_up'}</t>
+          <t>try_to_pick_it_up</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 'Try to pick it up'}</t>
+          <t>Try to pick it up</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_'call_for_help'}</t>
+          <t>call_for_help</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': 'Call for help'}</t>
+          <t>Call for help</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'text':_'help_the_person_slowly_and_carefully_back_away_from_the_snake'}</t>
+          <t>help_the_person_slowly_and_carefully_back_away_from_the_snake</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'text': 'Help the person slowly and carefully back away from the snake'}</t>
+          <t>Help the person slowly and carefully back away from the snake</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'text':_'stand_still_and_let_them_handle_it'}</t>
+          <t>stand_still_and_let_them_handle_it</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'text': 'Stand still and let them handle it'}</t>
+          <t>Stand still and let them handle it</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'text':_'run_away_from_the_scene'}</t>
+          <t>run_away_from_the_scene</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'text': 'Run away from the scene'}</t>
+          <t>Run away from the scene</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'text':_'stay_still_and_observe'}</t>
+          <t>stay_still_and_observe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'text': 'Stay still and observe'}</t>
+          <t>Stay still and observe</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'text':_'long_pants'}</t>
+          <t>long_pants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'text': 'Long pants'}</t>
+          <t>Long pants</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'text':_'long-sleeved_shirt'}</t>
+          <t>long-sleeved_shirt</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'text': 'Long-sleeved shirt'}</t>
+          <t>Long-sleeved shirt</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'text':_'closed-toed_boots'}</t>
+          <t>closed-toed_boots</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'text': 'Closed-toed boots'}</t>
+          <t>Closed-toed boots</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'text':_'gaiters'}</t>
+          <t>gaiters</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'text': 'Gaiters'}</t>
+          <t>Gaiters</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'text':_'wear_proper_gear_and_clothing'}</t>
+          <t>wear_proper_gear_and_clothing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'text': 'Wear proper gear and clothing'}</t>
+          <t>Wear proper gear and clothing</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'text':_'stay_on_designated_trails'}</t>
+          <t>stay_on_designated_trails</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'text': 'Stay on designated trails'}</t>
+          <t>Stay on designated trails</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'text':_'pay_attention_to_your_surroundings'}</t>
+          <t>pay_attention_to_your_surroundings</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'text': 'Pay attention to your surroundings'}</t>
+          <t>Pay attention to your surroundings</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'text':_'stay_with_a_group'}</t>
+          <t>stay_with_a_group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'text': 'Stay with a group'}</t>
+          <t>Stay with a group</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'text':_'call_a_professional_snake_removal_service'}</t>
+          <t>call_a_professional_snake_removal_service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'text': 'Call a professional snake removal service'}</t>
+          <t>Call a professional snake removal service</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'text':_'try_to_handle_it_yourself'}</t>
+          <t>try_to_handle_it_yourself</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'text': 'Try to handle it yourself'}</t>
+          <t>Try to handle it yourself</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'text':_'leave_it_alone_and_hope_it_goes_away'}</t>
+          <t>leave_it_alone_and_hope_it_goes_away</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'text': 'Leave it alone and hope it goes away'}</t>
+          <t>Leave it alone and hope it goes away</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'text':_'call_a_friend_or_family_member_for_help'}</t>
+          <t>call_a_friend_or_family_member_for_help</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'text': 'Call a friend or family member for help'}</t>
+          <t>Call a friend or family member for help</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'text':_'every_step'}</t>
+          <t>every_step</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'text': 'Every step'}</t>
+          <t>Every step</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'text':_'every_5_minutes'}</t>
+          <t>every_5_minutes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'text': 'Every 5 minutes'}</t>
+          <t>Every 5 minutes</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'text':_'every_10_minutes'}</t>
+          <t>every_10_minutes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'text': 'Every 10 minutes'}</t>
+          <t>Every 10 minutes</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'text':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'text': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'text':_'be_calm_and_stay_still'}</t>
+          <t>be_calm_and_stay_still</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'text': 'Be calm and stay still'}</t>
+          <t>Be calm and stay still</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'text':_'move_slowly_and_carefully'}</t>
+          <t>move_slowly_and_carefully</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'text': 'Move slowly and carefully'}</t>
+          <t>Move slowly and carefully</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'text':_'avoid_sudden_movements'}</t>
+          <t>avoid_sudden_movements</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'text': 'Avoid sudden movements'}</t>
+          <t>Avoid sudden movements</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'text':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'text': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'text':_'snake_awareness_quiz'}</t>
+          <t>snake_awareness_quiz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'text': 'Snake Awareness Quiz'}</t>
+          <t>Snake Awareness Quiz</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'text':_'snake_safety_quiz'}</t>
+          <t>snake_safety_quiz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'text': 'Snake Safety Quiz'}</t>
+          <t>Snake Safety Quiz</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'text':_'wild_animal_awareness_quiz'}</t>
+          <t>wild_animal_awareness_quiz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'text': 'Wild Animal Awareness Quiz'}</t>
+          <t>Wild Animal Awareness Quiz</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'text':_'outdoor_safety_quiz'}</t>
+          <t>outdoor_safety_quiz</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'text': 'Outdoor Safety Quiz'}</t>
+          <t>Outdoor Safety Quiz</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'text':_'to_learn_about_snakes_and_stay_safe'}</t>
+          <t>to_learn_about_snakes_and_stay_safe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'text': 'To learn about snakes and stay safe'}</t>
+          <t>To learn about snakes and stay safe</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'text':_'to_test_my_knowledge_about_snakes'}</t>
+          <t>to_test_my_knowledge_about_snakes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'text': 'To test my knowledge about snakes'}</t>
+          <t>To test my knowledge about snakes</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'text':_'to_help_others_learn_about_snakes'}</t>
+          <t>to_help_others_learn_about_snakes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'text': 'To help others learn about snakes'}</t>
+          <t>To help others learn about snakes</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'text':_'to_win_a_prize'}</t>
+          <t>to_win_a_prize</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'text': 'To win a prize'}</t>
+          <t>To win a prize</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'text':_'on_jotform'}</t>
+          <t>on_jotform</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'text': 'On Jotform'}</t>
+          <t>On Jotform</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'text':_'on_google'}</t>
+          <t>on_google</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'text': 'On Google'}</t>
+          <t>On Google</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'text':_'on_facebook'}</t>
+          <t>on_facebook</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'text': 'On Facebook'}</t>
+          <t>On Facebook</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'text':_'on_twitter'}</t>
+          <t>on_twitter</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'text': 'On Twitter'}</t>
+          <t>On Twitter</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'text':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'text': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'text':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'text': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'text':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'text': 'Not very likely'}</t>
+          <t>Not very likely</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'text':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'text': 'Not at all likely'}</t>
+          <t>Not at all likely</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'text':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'text': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'text':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'text': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'text':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'text': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'text':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'text': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'text':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'text': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'text':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'text': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'text':_'expert'}</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'text': 'Expert'}</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'text':_'recreation'}</t>
+          <t>recreation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'text': 'Recreation'}</t>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'text':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'text': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'text':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'text': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'text':_'eastern_coral_snake'}</t>
+          <t>eastern_coral_snake</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'text': 'Eastern Coral Snake'}</t>
+          <t>Eastern Coral Snake</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'text':_'western_diamondback_rattlesnake'}</t>
+          <t>western_diamondback_rattlesnake</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'text': 'Western Diamondback Rattlesnake'}</t>
+          <t>Western Diamondback Rattlesnake</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'text':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'text': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'text':_"to_respect_the_snakes'_space"}</t>
+          <t>to_respect_the_snakes'_space</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'text': "To respect the snakes' space"}</t>
+          <t>To respect the snakes' space</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'text':_'to_identify_the_snakes'}</t>
+          <t>to_identify_the_snakes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'text': 'To identify the snakes'}</t>
+          <t>To identify the snakes</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'text':_'to_handle_the_snakes'}</t>
+          <t>to_handle_the_snakes</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'text': 'To handle the snakes'}</t>
+          <t>To handle the snakes</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'text':_'to_leave_the_snakes_alone'}</t>
+          <t>to_leave_the_snakes_alone</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'text': 'To leave the snakes alone'}</t>
+          <t>To leave the snakes alone</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'text':_'first_time'}</t>
+          <t>first_time</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'text': 'First time'}</t>
+          <t>First time</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'text':_'second_time'}</t>
+          <t>second_time</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'text': 'Second time'}</t>
+          <t>Second time</t>
         </is>
       </c>
     </row>
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'text':_'third_time'}</t>
+          <t>third_time</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'text': 'Third time'}</t>
+          <t>Third time</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'text':_'more_than_three_times'}</t>
+          <t>more_than_three_times</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'text': 'More than three times'}</t>
+          <t>More than three times</t>
         </is>
       </c>
     </row>
